--- a/Outputs/Scenarios/PtX_demand_CY_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_CY_Electrification.xlsx
@@ -547,7 +547,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6.72325821059123e-10</v>
+        <v>6.723258210591231e-10</v>
       </c>
       <c r="I3" t="n">
         <v>1.880690975047868e-05</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001839548329654699</v>
+        <v>0.0018395483296547</v>
       </c>
       <c r="I10" t="n">
         <v>0.0006212458405224171</v>
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00454391460765182</v>
+        <v>0.004543914607651819</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0007573191012753035</v>
+        <v>0.0007573191012753034</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.003029276405101214</v>
+        <v>0.003029276405101213</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00454391460765182</v>
+        <v>0.004543914607651819</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0007573191012753035</v>
+        <v>0.0007573191012753034</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_CY_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_CY_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0007717492749563364</v>
+        <v>0.0008210627489166696</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0001286248791593894</v>
+        <v>0.0001704505912360756</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0005144995166375577</v>
+        <v>0.0006818023649443025</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0007717492749563364</v>
+        <v>0.0006818023649443025</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00106810233364894</v>
+        <v>0.00104861742087947</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.01046103196839486</v>
+        <v>0.01027019604475591</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0001286248791593894</v>
+        <v>0.0001704505912360756</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.004543914607651819</v>
+        <v>0.00443168195242908</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0007573191012753034</v>
+        <v>0.0009200061870526381</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.003029276405101213</v>
+        <v>0.003680024748210553</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.004543914607651819</v>
+        <v>0.003680024748210553</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0007573191012753034</v>
+        <v>0.0009200061870526381</v>
       </c>
     </row>
     <row r="43">
